--- a/frontend/public/templates/rtm-ems-log-amv-template.xlsx
+++ b/frontend/public/templates/rtm-ems-log-amv-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="Template" sheetId="1" r:id="rId1"/>
+    <sheet name="RTM Upload" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -13,288 +13,213 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Date:first day of the month/year</t>
+          <t>GRADE</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>202607</t>
+          <t>BALSAM</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>HEMLOCK</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CEDAR</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>CYPRESS</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>FIR</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>SPRUCE</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>PINE</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GRADE</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>BA</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CE</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CY</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>FI</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>PINE**</t>
-        </is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>10.25</v>
+      </c>
+      <c r="C2">
+        <v>20.50</v>
+      </c>
+      <c r="H2">
+        <v>30.75</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>10.25</v>
-      </c>
-      <c r="C3">
-        <v>20.50</v>
-      </c>
-      <c r="H3">
-        <v>30.75</v>
+          <t>B</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>J</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>K</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>U</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>X</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Q</t>
-        </is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>1.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B29">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
         <is>
           <t>6</t>
         </is>

--- a/frontend/public/templates/rtm-ems-log-amv-template.xlsx
+++ b/frontend/public/templates/rtm-ems-log-amv-template.xlsx
@@ -1,230 +1,694 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <sheets>
-    <sheet name="RTM Upload" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM Upload" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
 </workbook>
+</file>
+
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
+  <fonts count="2">
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAF7"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00A6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="00A6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="00A6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00A6A6A6"/>
+      </bottom>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
+</styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>GRADE</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>BALSAM</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>HEMLOCK</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>CEDAR</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>CYPRESS</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>FIR</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>SPRUCE</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>PINE</t>
-        </is>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Retrieval Date</t>
+        </is>
+      </c>
+      <c r="B1" s="2">
+        <f>TODAY()</f>
+        <v/>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>10.25</v>
-      </c>
-      <c r="C2">
-        <v>20.50</v>
-      </c>
-      <c r="H2">
-        <v>30.75</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Update Date</t>
+        </is>
+      </c>
+      <c r="B2" s="2">
+        <f>TODAY()</f>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>GRADE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>BALSAM</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>HEMLOCK</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CEDAR</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>CYPRESS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FIR</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>SPRUCE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>PINE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="C5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>30.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>B</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>C</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>D</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>E</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J</t>
+          <t>G</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>H</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>I</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>J</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>K</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>L</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Z</t>
+          <t>U</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B19">
-        <v>1.25</v>
+          <t>X</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Y</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Z</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/frontend/public/templates/rtm-ems-log-amv-template.xlsx
+++ b/frontend/public/templates/rtm-ems-log-amv-template.xlsx
@@ -454,23 +454,8 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Retrieval Date</t>
-        </is>
-      </c>
-      <c r="B1" s="2">
-        <f>TODAY()</f>
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
           <t>Update Date</t>
         </is>
-      </c>
-      <c r="B2" s="2">
-        <f>TODAY()</f>
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -521,15 +506,6 @@
           <t>A</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="C5" t="n">
-        <v>20.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>30.75</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -648,9 +624,6 @@
         <is>
           <t>1</t>
         </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1.25</v>
       </c>
     </row>
     <row r="23">

--- a/frontend/public/templates/rtm-ems-log-amv-template.xlsx
+++ b/frontend/public/templates/rtm-ems-log-amv-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM Upload" sheetId="1" r:id="R636bb0ed157047a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM Upload" sheetId="1" r:id="Rcc9b20c1ef2d4058"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -13,10 +13,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="1">
+  <x:numFmts count="2">
     <x:numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <x:numFmt numFmtId="200" formatCode="0.00"/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:color theme="1"/>
@@ -25,8 +26,31 @@
     <x:font>
       <x:b/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF161616"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF161616"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="FF0043CE"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="9">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -38,8 +62,38 @@
         <x:fgColor rgb="FFD9EAF7"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD6E7F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF4CE"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF5FF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF003366"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE8E8E8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="2">
+  <x:borders count="9">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -55,11 +109,97 @@
         <x:color rgb="FFA6A6A6"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FF8D8D8D"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FF8D8D8D"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FF8D8D8D"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FF8D8D8D"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFA6C8FF"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFA6C8FF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFA6C8FF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFA6C8FF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFA6C8FF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFA6C8FF"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFA6C8FF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFA6C8FF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFFFFFFF"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFC6C6C6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFC6C6C6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFC6C6C6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFC6C6C6"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD6D6D6"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD6D6D6"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD6D6D6"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD6D6D6"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="4">
+  <x:cellXfs count="41">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyAlignment="1">
       <x:alignment horizontal="left"/>
@@ -68,6 +208,75 @@
       <x:alignment horizontal="left"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="7" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="2" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="2" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="2" fillId="8" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="right" vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -359,228 +568,451 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="24" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="12" customWidth="1"/>
-    <x:col min="4" max="4" width="12" customWidth="1"/>
-    <x:col min="5" max="5" width="12" customWidth="1"/>
-    <x:col min="6" max="6" width="12" customWidth="1"/>
-    <x:col min="7" max="7" width="12" customWidth="1"/>
-    <x:col min="8" max="8" width="12" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="14" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="12" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="12" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="1" t="str">
-        <x:v>Update Date (YYYY-MM-DD)</x:v>
-      </x:c>
-      <x:c r="B1" s="3" t="str">
-        <x:v>Enter update date here</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GRADE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="B4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">BALSAM</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">HEMLOCK</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CEDAR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">CYPRESS</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">FIR</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">SPRUCE</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">PINE</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">A</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">B</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">C</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">D</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">E</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">F</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">G</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">H</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">I</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">J</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">K</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">L</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">M</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">U</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">X</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Y</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">Z</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">1</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">3</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">4</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">5</x:t>
-        </x:is>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">6</x:t>
-        </x:is>
-      </x:c>
+    <x:row r="1" ht="24" customHeight="1">
+      <x:c r="A1" s="8" t="str">
+        <x:v>Update Date (YYYY-MM-01)</x:v>
+      </x:c>
+      <x:c r="B1" s="13" t="str"/>
+      <x:c r="C1" s="4"/>
+      <x:c r="D1" s="4"/>
+      <x:c r="E1" s="4"/>
+      <x:c r="F1" s="4"/>
+      <x:c r="G1" s="4"/>
+      <x:c r="H1" s="4"/>
+      <x:c r="I1" s="4"/>
+      <x:c r="J1" s="4"/>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="8" t="str">
+        <x:v>Growth Indicator (O or S)</x:v>
+      </x:c>
+      <x:c r="B2" s="12" t="str"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+      <x:c r="H2" s="4"/>
+      <x:c r="I2" s="4"/>
+      <x:c r="J2" s="4"/>
+    </x:row>
+    <x:row r="3" ht="38" customHeight="1">
+      <x:c r="A3" s="22" t="str">
+        <x:v>Enter the first day of one month and select one growth type. Before April 2006, leave W, Z, 1, and 2 blank.</x:v>
+      </x:c>
+      <x:c r="B3" s="23"/>
+      <x:c r="C3" s="23"/>
+      <x:c r="D3" s="23"/>
+      <x:c r="E3" s="23"/>
+      <x:c r="F3" s="23"/>
+      <x:c r="G3" s="23"/>
+      <x:c r="H3" s="23"/>
+      <x:c r="I3" s="23"/>
+      <x:c r="J3" s="24"/>
+    </x:row>
+    <x:row r="4" ht="32" customHeight="1">
+      <x:c r="A4" s="30" t="str">
+        <x:v>GRADE</x:v>
+      </x:c>
+      <x:c r="B4" s="30" t="str">
+        <x:v>BALSAM</x:v>
+      </x:c>
+      <x:c r="C4" s="30" t="str">
+        <x:v>HEMLOCK</x:v>
+      </x:c>
+      <x:c r="D4" s="30" t="str">
+        <x:v>CEDAR</x:v>
+      </x:c>
+      <x:c r="E4" s="30" t="str">
+        <x:v>CYPRESS</x:v>
+      </x:c>
+      <x:c r="F4" s="30" t="str">
+        <x:v>FIR</x:v>
+      </x:c>
+      <x:c r="G4" s="30" t="str">
+        <x:v>SPRUCE</x:v>
+      </x:c>
+      <x:c r="H4" s="30" t="str">
+        <x:v>WH</x:v>
+      </x:c>
+      <x:c r="I4" s="30" t="str">
+        <x:v>LO</x:v>
+      </x:c>
+      <x:c r="J4" s="30" t="str">
+        <x:v>YE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="35" t="str">
+        <x:v>A</x:v>
+      </x:c>
+      <x:c r="B5" s="40"/>
+      <x:c r="C5" s="40"/>
+      <x:c r="D5" s="40"/>
+      <x:c r="E5" s="40"/>
+      <x:c r="F5" s="40"/>
+      <x:c r="G5" s="40"/>
+      <x:c r="H5" s="40"/>
+      <x:c r="I5" s="40"/>
+      <x:c r="J5" s="40"/>
+    </x:row>
+    <x:row r="6" ht="22" customHeight="1">
+      <x:c r="A6" s="35" t="str">
+        <x:v>B</x:v>
+      </x:c>
+      <x:c r="B6" s="40"/>
+      <x:c r="C6" s="40"/>
+      <x:c r="D6" s="40"/>
+      <x:c r="E6" s="40"/>
+      <x:c r="F6" s="40"/>
+      <x:c r="G6" s="40"/>
+      <x:c r="H6" s="40"/>
+      <x:c r="I6" s="40"/>
+      <x:c r="J6" s="40"/>
+    </x:row>
+    <x:row r="7" ht="22" customHeight="1">
+      <x:c r="A7" s="35" t="str">
+        <x:v>C</x:v>
+      </x:c>
+      <x:c r="B7" s="40"/>
+      <x:c r="C7" s="40"/>
+      <x:c r="D7" s="40"/>
+      <x:c r="E7" s="40"/>
+      <x:c r="F7" s="40"/>
+      <x:c r="G7" s="40"/>
+      <x:c r="H7" s="40"/>
+      <x:c r="I7" s="40"/>
+      <x:c r="J7" s="40"/>
+    </x:row>
+    <x:row r="8" ht="22" customHeight="1">
+      <x:c r="A8" s="35" t="str">
+        <x:v>D</x:v>
+      </x:c>
+      <x:c r="B8" s="40"/>
+      <x:c r="C8" s="40"/>
+      <x:c r="D8" s="40"/>
+      <x:c r="E8" s="40"/>
+      <x:c r="F8" s="40"/>
+      <x:c r="G8" s="40"/>
+      <x:c r="H8" s="40"/>
+      <x:c r="I8" s="40"/>
+      <x:c r="J8" s="40"/>
+    </x:row>
+    <x:row r="9" ht="22" customHeight="1">
+      <x:c r="A9" s="35" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="B9" s="40"/>
+      <x:c r="C9" s="40"/>
+      <x:c r="D9" s="40"/>
+      <x:c r="E9" s="40"/>
+      <x:c r="F9" s="40"/>
+      <x:c r="G9" s="40"/>
+      <x:c r="H9" s="40"/>
+      <x:c r="I9" s="40"/>
+      <x:c r="J9" s="40"/>
+    </x:row>
+    <x:row r="10" ht="22" customHeight="1">
+      <x:c r="A10" s="35" t="str">
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="B10" s="40"/>
+      <x:c r="C10" s="40"/>
+      <x:c r="D10" s="40"/>
+      <x:c r="E10" s="40"/>
+      <x:c r="F10" s="40"/>
+      <x:c r="G10" s="40"/>
+      <x:c r="H10" s="40"/>
+      <x:c r="I10" s="40"/>
+      <x:c r="J10" s="40"/>
+    </x:row>
+    <x:row r="11" ht="22" customHeight="1">
+      <x:c r="A11" s="35" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="B11" s="40"/>
+      <x:c r="C11" s="40"/>
+      <x:c r="D11" s="40"/>
+      <x:c r="E11" s="40"/>
+      <x:c r="F11" s="40"/>
+      <x:c r="G11" s="40"/>
+      <x:c r="H11" s="40"/>
+      <x:c r="I11" s="40"/>
+      <x:c r="J11" s="40"/>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="35" t="str">
+        <x:v>H</x:v>
+      </x:c>
+      <x:c r="B12" s="40"/>
+      <x:c r="C12" s="40"/>
+      <x:c r="D12" s="40"/>
+      <x:c r="E12" s="40"/>
+      <x:c r="F12" s="40"/>
+      <x:c r="G12" s="40"/>
+      <x:c r="H12" s="40"/>
+      <x:c r="I12" s="40"/>
+      <x:c r="J12" s="40"/>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="35" t="str">
+        <x:v>I</x:v>
+      </x:c>
+      <x:c r="B13" s="40"/>
+      <x:c r="C13" s="40"/>
+      <x:c r="D13" s="40"/>
+      <x:c r="E13" s="40"/>
+      <x:c r="F13" s="40"/>
+      <x:c r="G13" s="40"/>
+      <x:c r="H13" s="40"/>
+      <x:c r="I13" s="40"/>
+      <x:c r="J13" s="40"/>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="35" t="str">
+        <x:v>J</x:v>
+      </x:c>
+      <x:c r="B14" s="40"/>
+      <x:c r="C14" s="40"/>
+      <x:c r="D14" s="40"/>
+      <x:c r="E14" s="40"/>
+      <x:c r="F14" s="40"/>
+      <x:c r="G14" s="40"/>
+      <x:c r="H14" s="40"/>
+      <x:c r="I14" s="40"/>
+      <x:c r="J14" s="40"/>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="35" t="str">
+        <x:v>K</x:v>
+      </x:c>
+      <x:c r="B15" s="40"/>
+      <x:c r="C15" s="40"/>
+      <x:c r="D15" s="40"/>
+      <x:c r="E15" s="40"/>
+      <x:c r="F15" s="40"/>
+      <x:c r="G15" s="40"/>
+      <x:c r="H15" s="40"/>
+      <x:c r="I15" s="40"/>
+      <x:c r="J15" s="40"/>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="35" t="str">
+        <x:v>L</x:v>
+      </x:c>
+      <x:c r="B16" s="40"/>
+      <x:c r="C16" s="40"/>
+      <x:c r="D16" s="40"/>
+      <x:c r="E16" s="40"/>
+      <x:c r="F16" s="40"/>
+      <x:c r="G16" s="40"/>
+      <x:c r="H16" s="40"/>
+      <x:c r="I16" s="40"/>
+      <x:c r="J16" s="40"/>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="35" t="str">
+        <x:v>M</x:v>
+      </x:c>
+      <x:c r="B17" s="40"/>
+      <x:c r="C17" s="40"/>
+      <x:c r="D17" s="40"/>
+      <x:c r="E17" s="40"/>
+      <x:c r="F17" s="40"/>
+      <x:c r="G17" s="40"/>
+      <x:c r="H17" s="40"/>
+      <x:c r="I17" s="40"/>
+      <x:c r="J17" s="40"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="35" t="str">
+        <x:v>U</x:v>
+      </x:c>
+      <x:c r="B18" s="40"/>
+      <x:c r="C18" s="40"/>
+      <x:c r="D18" s="40"/>
+      <x:c r="E18" s="40"/>
+      <x:c r="F18" s="40"/>
+      <x:c r="G18" s="40"/>
+      <x:c r="H18" s="40"/>
+      <x:c r="I18" s="40"/>
+      <x:c r="J18" s="40"/>
+    </x:row>
+    <x:row r="19" ht="22" customHeight="1">
+      <x:c r="A19" s="35" t="str">
+        <x:v>W</x:v>
+      </x:c>
+      <x:c r="B19" s="40"/>
+      <x:c r="C19" s="40"/>
+      <x:c r="D19" s="40"/>
+      <x:c r="E19" s="40"/>
+      <x:c r="F19" s="40"/>
+      <x:c r="G19" s="40"/>
+      <x:c r="H19" s="40"/>
+      <x:c r="I19" s="40"/>
+      <x:c r="J19" s="40"/>
+    </x:row>
+    <x:row r="20" ht="22" customHeight="1">
+      <x:c r="A20" s="35" t="str">
+        <x:v>X</x:v>
+      </x:c>
+      <x:c r="B20" s="40"/>
+      <x:c r="C20" s="40"/>
+      <x:c r="D20" s="40"/>
+      <x:c r="E20" s="40"/>
+      <x:c r="F20" s="40"/>
+      <x:c r="G20" s="40"/>
+      <x:c r="H20" s="40"/>
+      <x:c r="I20" s="40"/>
+      <x:c r="J20" s="40"/>
+    </x:row>
+    <x:row r="21" ht="22" customHeight="1">
+      <x:c r="A21" s="35" t="str">
+        <x:v>Y</x:v>
+      </x:c>
+      <x:c r="B21" s="40"/>
+      <x:c r="C21" s="40"/>
+      <x:c r="D21" s="40"/>
+      <x:c r="E21" s="40"/>
+      <x:c r="F21" s="40"/>
+      <x:c r="G21" s="40"/>
+      <x:c r="H21" s="40"/>
+      <x:c r="I21" s="40"/>
+      <x:c r="J21" s="40"/>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22" s="35" t="str">
+        <x:v>Z</x:v>
+      </x:c>
+      <x:c r="B22" s="40"/>
+      <x:c r="C22" s="40"/>
+      <x:c r="D22" s="40"/>
+      <x:c r="E22" s="40"/>
+      <x:c r="F22" s="40"/>
+      <x:c r="G22" s="40"/>
+      <x:c r="H22" s="40"/>
+      <x:c r="I22" s="40"/>
+      <x:c r="J22" s="40"/>
+    </x:row>
+    <x:row r="23" ht="22" customHeight="1">
+      <x:c r="A23" s="35" t="str">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B23" s="40"/>
+      <x:c r="C23" s="40"/>
+      <x:c r="D23" s="40"/>
+      <x:c r="E23" s="40"/>
+      <x:c r="F23" s="40"/>
+      <x:c r="G23" s="40"/>
+      <x:c r="H23" s="40"/>
+      <x:c r="I23" s="40"/>
+      <x:c r="J23" s="40"/>
+    </x:row>
+    <x:row r="24" ht="22" customHeight="1">
+      <x:c r="A24" s="35" t="str">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B24" s="40"/>
+      <x:c r="C24" s="40"/>
+      <x:c r="D24" s="40"/>
+      <x:c r="E24" s="40"/>
+      <x:c r="F24" s="40"/>
+      <x:c r="G24" s="40"/>
+      <x:c r="H24" s="40"/>
+      <x:c r="I24" s="40"/>
+      <x:c r="J24" s="40"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="35" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B25" s="40"/>
+      <x:c r="C25" s="40"/>
+      <x:c r="D25" s="40"/>
+      <x:c r="E25" s="40"/>
+      <x:c r="F25" s="40"/>
+      <x:c r="G25" s="40"/>
+      <x:c r="H25" s="40"/>
+      <x:c r="I25" s="40"/>
+      <x:c r="J25" s="40"/>
+    </x:row>
+    <x:row r="26" ht="22" customHeight="1">
+      <x:c r="A26" s="35" t="str">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B26" s="40"/>
+      <x:c r="C26" s="40"/>
+      <x:c r="D26" s="40"/>
+      <x:c r="E26" s="40"/>
+      <x:c r="F26" s="40"/>
+      <x:c r="G26" s="40"/>
+      <x:c r="H26" s="40"/>
+      <x:c r="I26" s="40"/>
+      <x:c r="J26" s="40"/>
+    </x:row>
+    <x:row r="27" ht="22" customHeight="1">
+      <x:c r="A27" s="35" t="str">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B27" s="40"/>
+      <x:c r="C27" s="40"/>
+      <x:c r="D27" s="40"/>
+      <x:c r="E27" s="40"/>
+      <x:c r="F27" s="40"/>
+      <x:c r="G27" s="40"/>
+      <x:c r="H27" s="40"/>
+      <x:c r="I27" s="40"/>
+      <x:c r="J27" s="40"/>
+    </x:row>
+    <x:row r="28" ht="22" customHeight="1">
+      <x:c r="A28" s="35" t="str">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B28" s="40"/>
+      <x:c r="C28" s="40"/>
+      <x:c r="D28" s="40"/>
+      <x:c r="E28" s="40"/>
+      <x:c r="F28" s="40"/>
+      <x:c r="G28" s="40"/>
+      <x:c r="H28" s="40"/>
+      <x:c r="I28" s="40"/>
+      <x:c r="J28" s="40"/>
+    </x:row>
+    <x:row r="29" ht="22" customHeight="1">
+      <x:c r="A29" s="35" t="str">
+        <x:v>BLANK</x:v>
+      </x:c>
+      <x:c r="B29" s="40"/>
+      <x:c r="C29" s="40"/>
+      <x:c r="D29" s="40"/>
+      <x:c r="E29" s="40"/>
+      <x:c r="F29" s="40"/>
+      <x:c r="G29" s="40"/>
+      <x:c r="H29" s="40"/>
+      <x:c r="I29" s="40"/>
+      <x:c r="J29" s="40"/>
     </x:row>
   </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A3:J3"/>
+  </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="B2">
+      <x:formula1>"O,S"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
--- a/frontend/public/templates/rtm-ems-log-amv-template.xlsx
+++ b/frontend/public/templates/rtm-ems-log-amv-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Average market values" sheetId="1" r:id="R2ade46001d384e21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Average market values" sheetId="1" r:id="R4de123c7489d4333"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -421,7 +421,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="9" t="str">
-        <x:v>Enter values for one month. Choose the effective month on the upload screen.</x:v>
+        <x:v>Enter values for the effective month shown on the upload screen.</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>

--- a/frontend/public/templates/rtm-ems-log-amv-template.xlsx
+++ b/frontend/public/templates/rtm-ems-log-amv-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Average market values" sheetId="1" r:id="R4de123c7489d4333"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Average market values" sheetId="1" r:id="R5275c03016df4281"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -421,7 +421,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="9" t="str">
-        <x:v>Enter values for the effective month shown on the upload screen.</x:v>
+        <x:v>Enter values for one month. Choose the effective month on the upload screen.</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>
@@ -459,7 +459,7 @@
     </x:row>
     <x:row r="3" ht="24" customHeight="1">
       <x:c r="A3" s="22" t="str">
-        <x:v>A</x:v>
+        <x:v>B</x:v>
       </x:c>
       <x:c r="B3" s="28"/>
       <x:c r="C3" s="28"/>
@@ -471,7 +471,7 @@
     </x:row>
     <x:row r="4" ht="24" customHeight="1">
       <x:c r="A4" s="22" t="str">
-        <x:v>B</x:v>
+        <x:v>C</x:v>
       </x:c>
       <x:c r="B4" s="28"/>
       <x:c r="C4" s="28"/>
@@ -483,7 +483,7 @@
     </x:row>
     <x:row r="5" ht="24" customHeight="1">
       <x:c r="A5" s="22" t="str">
-        <x:v>C</x:v>
+        <x:v>D</x:v>
       </x:c>
       <x:c r="B5" s="28"/>
       <x:c r="C5" s="28"/>
@@ -495,7 +495,7 @@
     </x:row>
     <x:row r="6" ht="24" customHeight="1">
       <x:c r="A6" s="22" t="str">
-        <x:v>D</x:v>
+        <x:v>E</x:v>
       </x:c>
       <x:c r="B6" s="28"/>
       <x:c r="C6" s="28"/>
@@ -507,7 +507,7 @@
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
       <x:c r="A7" s="22" t="str">
-        <x:v>E</x:v>
+        <x:v>F</x:v>
       </x:c>
       <x:c r="B7" s="28"/>
       <x:c r="C7" s="28"/>
@@ -519,7 +519,7 @@
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
       <x:c r="A8" s="22" t="str">
-        <x:v>F</x:v>
+        <x:v>G</x:v>
       </x:c>
       <x:c r="B8" s="28"/>
       <x:c r="C8" s="28"/>
@@ -531,7 +531,7 @@
     </x:row>
     <x:row r="9" ht="24" customHeight="1">
       <x:c r="A9" s="22" t="str">
-        <x:v>G</x:v>
+        <x:v>H</x:v>
       </x:c>
       <x:c r="B9" s="28"/>
       <x:c r="C9" s="28"/>
@@ -543,7 +543,7 @@
     </x:row>
     <x:row r="10" ht="24" customHeight="1">
       <x:c r="A10" s="22" t="str">
-        <x:v>H</x:v>
+        <x:v>I</x:v>
       </x:c>
       <x:c r="B10" s="28"/>
       <x:c r="C10" s="28"/>
@@ -555,7 +555,7 @@
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
       <x:c r="A11" s="22" t="str">
-        <x:v>I</x:v>
+        <x:v>J</x:v>
       </x:c>
       <x:c r="B11" s="28"/>
       <x:c r="C11" s="28"/>
@@ -567,7 +567,7 @@
     </x:row>
     <x:row r="12" ht="24" customHeight="1">
       <x:c r="A12" s="22" t="str">
-        <x:v>J</x:v>
+        <x:v>K</x:v>
       </x:c>
       <x:c r="B12" s="28"/>
       <x:c r="C12" s="28"/>
@@ -579,7 +579,7 @@
     </x:row>
     <x:row r="13" ht="24" customHeight="1">
       <x:c r="A13" s="22" t="str">
-        <x:v>K</x:v>
+        <x:v>L</x:v>
       </x:c>
       <x:c r="B13" s="28"/>
       <x:c r="C13" s="28"/>
@@ -591,7 +591,7 @@
     </x:row>
     <x:row r="14" ht="24" customHeight="1">
       <x:c r="A14" s="22" t="str">
-        <x:v>L</x:v>
+        <x:v>M</x:v>
       </x:c>
       <x:c r="B14" s="28"/>
       <x:c r="C14" s="28"/>
@@ -603,7 +603,7 @@
     </x:row>
     <x:row r="15" ht="24" customHeight="1">
       <x:c r="A15" s="22" t="str">
-        <x:v>M</x:v>
+        <x:v>U</x:v>
       </x:c>
       <x:c r="B15" s="28"/>
       <x:c r="C15" s="28"/>
@@ -615,7 +615,7 @@
     </x:row>
     <x:row r="16" ht="24" customHeight="1">
       <x:c r="A16" s="22" t="str">
-        <x:v>U</x:v>
+        <x:v>X</x:v>
       </x:c>
       <x:c r="B16" s="28"/>
       <x:c r="C16" s="28"/>
@@ -627,7 +627,7 @@
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
       <x:c r="A17" s="22" t="str">
-        <x:v>X</x:v>
+        <x:v>Y</x:v>
       </x:c>
       <x:c r="B17" s="28"/>
       <x:c r="C17" s="28"/>
@@ -637,18 +637,6 @@
       <x:c r="G17" s="28"/>
       <x:c r="H17" s="28"/>
     </x:row>
-    <x:row r="18" ht="24" customHeight="1">
-      <x:c r="A18" s="22" t="str">
-        <x:v>Y</x:v>
-      </x:c>
-      <x:c r="B18" s="28"/>
-      <x:c r="C18" s="28"/>
-      <x:c r="D18" s="28"/>
-      <x:c r="E18" s="28"/>
-      <x:c r="F18" s="28"/>
-      <x:c r="G18" s="28"/>
-      <x:c r="H18" s="28"/>
-    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H1"/>

--- a/frontend/public/templates/rtm-ems-log-amv-template.xlsx
+++ b/frontend/public/templates/rtm-ems-log-amv-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Average market values" sheetId="1" r:id="R5275c03016df4281"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Average market values" sheetId="1" r:id="Rc430822f65c54023"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -421,7 +421,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="9" t="str">
-        <x:v>Enter values for one month. Choose the effective month on the upload screen.</x:v>
+        <x:v>Enter values for month.</x:v>
       </x:c>
       <x:c r="B1" s="10"/>
       <x:c r="C1" s="10"/>
